--- a/Personal_Budget.xlsx
+++ b/Personal_Budget.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyStuff\Income And Expense Forecast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2A6F35-2368-4DB5-B2E6-E8D467B1A5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1BE8D6-2315-834B-92D7-AC930D683BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="19954" windowHeight="12652" xr2:uid="{6AE57E8B-8FFC-40E8-899B-112AE5CB0BEC}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="19960" windowHeight="12660" xr2:uid="{6AE57E8B-8FFC-40E8-899B-112AE5CB0BEC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,11 +182,6 @@
     <t>S-Class Saloon Long S500L</t>
   </si>
   <si>
-    <t xml:space="preserve">Others not specify per month 
-~ Denzer D9 Highway (80 km/day) ~HKD $18/day
-~ S-Class Saloon Long </t>
-  </si>
-  <si>
     <t>S-Class Saloon Long
 ~ HKD $11,329 per year 
 ~Insurance $12,000–$40,000 avg $26000
@@ -197,6 +192,11 @@
     <t>First Registration Tax (FRT) — One‑time when buying the car
 ~ S-Class Saloon Long HKD $0
 FRT is already included in the showroom price, so you don’t pay extra at purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others not specify per month 
+~ Denzer D9 Highway (80 km/day) ~HKD $18/day
+~ S-Class Saloon Long ~HKD $115/day </t>
   </si>
 </sst>
 </file>
@@ -344,50 +344,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -395,39 +425,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -765,32 +762,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161E1676-8615-4F40-9CAB-FCD773F668D5}">
   <dimension ref="A1:K56"/>
-  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="8.69140625" style="20"/>
-    <col min="6" max="6" width="17.84375" style="20" customWidth="1"/>
-    <col min="7" max="7" width="31.921875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="8.69140625" style="20"/>
-    <col min="9" max="9" width="16" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.69140625" style="20"/>
+    <col min="1" max="5" width="8.6640625" style="8"/>
+    <col min="6" max="6" width="17.83203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="32" style="8" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" style="8"/>
+    <col min="9" max="9" width="16" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+    </row>
+    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="13"/>
@@ -799,138 +796,138 @@
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="3">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="39.549999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="8">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="3">
         <f>G2-SUM(G12:G15)-SUM(G54:G56)-SUM(G46:G48)-SUM(G22:G23)-G27</f>
         <v>731414745.45000005</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="3">
         <f>G20/12+G21/12+G34+SUM(G35:G38)+G24+G26/12+G28</f>
-        <v>160282.5</v>
-      </c>
-      <c r="I4" s="21"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+        <v>163732.5</v>
+      </c>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="3">
         <f>SUM(G39:G41)+G25</f>
         <v>422948</v>
       </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A6" s="22" t="s">
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="8">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="3">
         <f>G4*12 + G5</f>
-        <v>2346338</v>
-      </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="25"/>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+        <v>2387738</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A11" s="10" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="26"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="8">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="3">
         <v>250000000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="8">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="3">
         <v>825000</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="13"/>
@@ -938,275 +935,275 @@
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="14"/>
-      <c r="G14" s="8">
+      <c r="G14" s="3">
         <v>1780000</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="8">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="3">
         <v>12000000</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A19" s="10" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="2" t="s">
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="8">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="3">
         <f>25000*12</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="8">
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="3">
         <f>100000*12</f>
         <v>1200000</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="283.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:11" ht="283.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="8">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="3">
         <f>901000*3</f>
         <v>2703000</v>
       </c>
-      <c r="K22" s="27"/>
-    </row>
-    <row r="23" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="2" t="s">
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="8">
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="3">
         <f>188000 * 3</f>
         <v>564000</v>
       </c>
-      <c r="K23" s="27"/>
-    </row>
-    <row r="24" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="2" t="s">
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="8">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="3">
         <v>25000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="8">
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="3">
         <v>127500</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="142.30000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:11" ht="142.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="8">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="3">
         <f>7550*3</f>
         <v>22650</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="48.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:11" ht="48.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="8">
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="3">
         <f>32500*3</f>
         <v>97500</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="78.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="8">
-        <f>18 * 30</f>
-        <v>540</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A31" s="7" t="s">
+    <row r="28" spans="1:11" ht="79" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="3">
+        <f>(18 * 30) + (115 * 30)</f>
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A33" s="10" t="s">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="11"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A34" s="2" t="s">
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="12">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="6">
         <f>5722</f>
         <v>5722</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="59.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:7" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="12">
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="6">
         <v>1500</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="54.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:7" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="12">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="6">
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="2" t="s">
+    <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="12">
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="6">
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="58.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:7" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B38" s="13"/>
@@ -1214,91 +1211,91 @@
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
       <c r="F38" s="14"/>
-      <c r="G38" s="12">
+      <c r="G38" s="6">
         <v>203</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="46.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
+    <row r="39" spans="1:7" ht="46.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="12">
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="6">
         <v>220000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
+    <row r="40" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="B40" s="13"/>
       <c r="C40" s="13"/>
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="14"/>
-      <c r="G40" s="12">
+      <c r="G40" s="6">
         <v>54829</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="92.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="2" t="s">
+    <row r="41" spans="1:7" ht="92.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="12">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="6">
         <v>20619</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" s="7" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A45" s="15" t="s">
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="18"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A46" s="5" t="s">
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="12" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="13"/>
@@ -1306,13 +1303,13 @@
       <c r="D46" s="13"/>
       <c r="E46" s="13"/>
       <c r="F46" s="14"/>
-      <c r="G46" s="12">
+      <c r="G46" s="6">
         <f>19800</f>
         <v>19800</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B47" s="13"/>
@@ -1320,105 +1317,104 @@
       <c r="D47" s="13"/>
       <c r="E47" s="13"/>
       <c r="F47" s="14"/>
-      <c r="G47" s="12">
+      <c r="G47" s="6">
         <v>60000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="12">
+    <row r="48" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A51" s="7" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-    </row>
-    <row r="53" spans="1:7" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A53" s="10" t="s">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="22"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A54" s="2" t="s">
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="8">
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="3">
         <v>527824.55000000005</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="8">
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="3">
         <v>8130</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="8"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A51:G52"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G10"/>
     <mergeCell ref="A17:G18"/>
@@ -1433,23 +1429,24 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A51:G52"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A43:G44"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A39:F39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Personal_Budget.xlsx
+++ b/Personal_Budget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1BE8D6-2315-834B-92D7-AC930D683BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351C9569-3421-5346-8226-548587514BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="19960" windowHeight="12660" xr2:uid="{6AE57E8B-8FFC-40E8-899B-112AE5CB0BEC}"/>
   </bookViews>
@@ -182,21 +182,21 @@
     <t>S-Class Saloon Long S500L</t>
   </si>
   <si>
+    <t>First Registration Tax (FRT) — One‑time when buying the car
+~ S-Class Saloon Long HKD $0
+FRT is already included in the showroom price, so you don’t pay extra at purchase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Others not specify per month 
+~ Denzer D9 Highway (80 km/day) ~HKD $18/day
+~ S-Class Saloon Long ~HKD $115/day </t>
+  </si>
+  <si>
     <t>S-Class Saloon Long
-~ HKD $11,329 per year 
+~ HKD $5,929 per year 
 ~Insurance $12,000–$40,000 avg $26000
 ~Maintenance $8,000–$15,000 avg $11,500
 ~ Tyres (amortized) $4,000–$8,000 avg $6000</t>
-  </si>
-  <si>
-    <t>First Registration Tax (FRT) — One‑time when buying the car
-~ S-Class Saloon Long HKD $0
-FRT is already included in the showroom price, so you don’t pay extra at purchase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Others not specify per month 
-~ Denzer D9 Highway (80 km/day) ~HKD $18/day
-~ S-Class Saloon Long ~HKD $115/day </t>
   </si>
 </sst>
 </file>
@@ -379,6 +379,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -388,6 +403,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -398,24 +416,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,26 +773,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
@@ -801,28 +801,28 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
       <c r="G3" s="3">
         <f>G2-SUM(G12:G15)-SUM(G54:G56)-SUM(G46:G48)-SUM(G22:G23)-G27</f>
         <v>731414745.45000005</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
       <c r="G4" s="3">
         <f>G20/12+G21/12+G34+SUM(G35:G38)+G24+G26/12+G28</f>
         <v>163732.5</v>
@@ -830,32 +830,32 @@
       <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
       <c r="G5" s="3">
         <f>SUM(G39:G41)+G25</f>
-        <v>422948</v>
+        <v>417548</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="3">
         <f>G4*12 + G5</f>
-        <v>2387738</v>
+        <v>2382338</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -870,156 +870,156 @@
       <c r="I7" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="3">
         <v>250000000</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="3">
         <v>825000</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="3">
         <v>1780000</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="3">
         <v>12000000</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="3">
         <f>25000*12</f>
         <v>300000</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="3">
         <f>100000*12</f>
         <v>1200000</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="283.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="3">
         <f>901000*3</f>
         <v>2703000</v>
@@ -1027,14 +1027,14 @@
       <c r="K22" s="10"/>
     </row>
     <row r="23" spans="1:11" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="3">
         <f>188000 * 3</f>
         <v>564000</v>
@@ -1042,68 +1042,68 @@
       <c r="K23" s="10"/>
     </row>
     <row r="24" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="3">
         <v>25000</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
       <c r="G25" s="3">
         <v>127500</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="142.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
       <c r="G26" s="3">
         <f>7550*3</f>
         <v>22650</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="48.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
       <c r="G27" s="3">
         <f>32500*3</f>
         <v>97500</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="79" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="A28" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
       <c r="G28" s="3">
         <f>(18 * 30) + (115 * 30)</f>
         <v>3990</v>
@@ -1119,137 +1119,137 @@
       <c r="G29" s="4"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="5"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
       <c r="G34" s="6">
         <f>5722</f>
         <v>5722</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="59.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
       <c r="G35" s="6">
         <v>1500</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
       <c r="G36" s="6">
         <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
       <c r="G37" s="6">
         <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="58.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="14"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19"/>
       <c r="G38" s="6">
         <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="46.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
       <c r="G39" s="6">
         <v>220000</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="14"/>
+      <c r="A40" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="6">
-        <v>54829</v>
+        <v>49429</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="92.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
       <c r="G41" s="6">
         <v>20619</v>
       </c>
@@ -1264,24 +1264,24 @@
       <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="25" t="s">
@@ -1295,126 +1295,131 @@
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="14"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="19"/>
       <c r="G46" s="6">
         <f>19800</f>
         <v>19800</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="14"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="6">
         <v>60000</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="78" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
+      <c r="A48" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="22"/>
-      <c r="C51" s="22"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="18" t="s">
+      <c r="A54" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
       <c r="G54" s="3">
         <v>527824.55000000005</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="18" t="s">
+      <c r="A55" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
       <c r="G55" s="3">
         <v>8130</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
       <c r="G56" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A51:G52"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A43:G44"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A9:G10"/>
     <mergeCell ref="A17:G18"/>
@@ -1431,22 +1436,17 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A43:G44"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A51:G52"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
